--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -1,46 +1,181 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C470EA2C-86E0-440F-8AF4-C26CB9622248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1380" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="case_matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'case_matrix'!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$W$2</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>case_id</t>
+  </si>
+  <si>
+    <t>case_group</t>
+  </si>
+  <si>
+    <t>use_for_model</t>
+  </si>
+  <si>
+    <t>thermal_case</t>
+  </si>
+  <si>
+    <t>orbit_case</t>
+  </si>
+  <si>
+    <t>beta_angle_deg</t>
+  </si>
+  <si>
+    <t>sun_direction_body</t>
+  </si>
+  <si>
+    <t>duration_s</t>
+  </si>
+  <si>
+    <t>sample_interval_s</t>
+  </si>
+  <si>
+    <t>power_mode</t>
+  </si>
+  <si>
+    <t>lct_heat_w</t>
+  </si>
+  <si>
+    <t>stt_heat_w</t>
+  </si>
+  <si>
+    <t>pcdu_heat_w</t>
+  </si>
+  <si>
+    <t>stt_location</t>
+  </si>
+  <si>
+    <t>lct_location</t>
+  </si>
+  <si>
+    <t>constraint_set</t>
+  </si>
+  <si>
+    <t>td_output_path</t>
+  </si>
+  <si>
+    <t>femap_model_path</t>
+  </si>
+  <si>
+    <t>femap_result_path</t>
+  </si>
+  <si>
+    <t>femap_loadset_start</t>
+  </si>
+  <si>
+    <t>femap_loadset_end</t>
+  </si>
+  <si>
+    <t>python_result_path</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>TD001_lct_heat_beta30_acq</t>
+  </si>
+  <si>
+    <t>sensitivity</t>
+  </si>
+  <si>
+    <t>exclude</t>
+  </si>
+  <si>
+    <t>local_heat</t>
+  </si>
+  <si>
+    <t>leo_3orbit_nominal</t>
+  </si>
+  <si>
+    <t>MZ</t>
+  </si>
+  <si>
+    <t>acquisition</t>
+  </si>
+  <si>
+    <t>PZ_center</t>
+  </si>
+  <si>
+    <t>MZ_center</t>
+  </si>
+  <si>
+    <t>stt_near_321</t>
+  </si>
+  <si>
+    <t>data/td_raw/TD001_lct_heat_beta30_acq/output_all_time.dat</t>
+  </si>
+  <si>
+    <t>data/femap_raw/TD001_lct_heat_beta30_acq/model.modfem</t>
+  </si>
+  <si>
+    <t>data/femap_raw/TD001_lct_heat_beta30_acq/translation_rotation.xlsx</t>
+  </si>
+  <si>
+    <t>results/TD001_lct_heat_beta30_acq/los_angles.csv</t>
+  </si>
+  <si>
+    <t>Example: 3-orbit LEO case with local LCT heat, exported every 600 s. Use STT-relative LOS as main target.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,83 +192,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,259 +497,178 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="42" customWidth="1" min="18" max="18"/>
-    <col width="42" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
-    <col width="42" customWidth="1" min="23" max="23"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="17.75" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="21.875" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="21.625" customWidth="1"/>
+    <col min="10" max="10" width="15.25" customWidth="1"/>
+    <col min="11" max="11" width="16.875" customWidth="1"/>
+    <col min="12" max="12" width="16.375" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="14" max="14" width="18.625" customWidth="1"/>
+    <col min="15" max="15" width="17.75" customWidth="1"/>
+    <col min="16" max="16" width="21" customWidth="1"/>
+    <col min="17" max="19" width="42" customWidth="1"/>
+    <col min="20" max="20" width="24.375" customWidth="1"/>
+    <col min="21" max="21" width="23.5" customWidth="1"/>
+    <col min="22" max="23" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>case_group</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>use_for_model</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>thermal_case</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>orbit_case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>beta_angle_deg</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>sun_direction_body</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>duration_s</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>sample_interval_s</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>power_mode</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>lct_heat_w</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>stt_heat_w</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>pcdu_heat_w</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>stt_location</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>lct_location</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>constraint_set</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>td_output_path</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>femap_model_path</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>femap_result_path</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>femap_loadset_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>femap_loadset_end</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>python_result_path</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TD001_lct_heat_beta30_acq</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>sensitivity</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>exclude</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>local_heat</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>leo_3orbit_nominal</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
         <v>30</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MZ</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
         <v>16200</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>600</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>acquisition</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2">
         <v>8</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>12</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>PZ_center</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>MZ_center</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>stt_near_321</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>data/td_raw/TD001_lct_heat_beta30_acq/output_all_time.dat</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>data/femap_raw/TD001_lct_heat_beta30_acq/model.modfem</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>data/femap_raw/TD001_lct_heat_beta30_acq/translation_rotation.xlsx</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>32</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>results/TD001_lct_heat_beta30_acq/los_angles.csv</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Example: 3-orbit LEO case with local LCT heat, exported every 600 s. Use STT-relative LOS as main target.</t>
-        </is>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W2"/>
+  <autoFilter ref="A1:W2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -1,174 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C470EA2C-86E0-440F-8AF4-C26CB9622248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1380" yWindow="2310" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
+    <sheet name="case_matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'case_matrix'!$A$1:$W$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <si>
-    <t>case_id</t>
-  </si>
-  <si>
-    <t>case_group</t>
-  </si>
-  <si>
-    <t>use_for_model</t>
-  </si>
-  <si>
-    <t>thermal_case</t>
-  </si>
-  <si>
-    <t>orbit_case</t>
-  </si>
-  <si>
-    <t>beta_angle_deg</t>
-  </si>
-  <si>
-    <t>sun_direction_body</t>
-  </si>
-  <si>
-    <t>duration_s</t>
-  </si>
-  <si>
-    <t>sample_interval_s</t>
-  </si>
-  <si>
-    <t>power_mode</t>
-  </si>
-  <si>
-    <t>lct_heat_w</t>
-  </si>
-  <si>
-    <t>stt_heat_w</t>
-  </si>
-  <si>
-    <t>pcdu_heat_w</t>
-  </si>
-  <si>
-    <t>stt_location</t>
-  </si>
-  <si>
-    <t>lct_location</t>
-  </si>
-  <si>
-    <t>constraint_set</t>
-  </si>
-  <si>
-    <t>td_output_path</t>
-  </si>
-  <si>
-    <t>femap_model_path</t>
-  </si>
-  <si>
-    <t>femap_result_path</t>
-  </si>
-  <si>
-    <t>femap_loadset_start</t>
-  </si>
-  <si>
-    <t>femap_loadset_end</t>
-  </si>
-  <si>
-    <t>python_result_path</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>TD001_lct_heat_beta30_acq</t>
-  </si>
-  <si>
-    <t>sensitivity</t>
-  </si>
-  <si>
-    <t>exclude</t>
-  </si>
-  <si>
-    <t>local_heat</t>
-  </si>
-  <si>
-    <t>leo_3orbit_nominal</t>
-  </si>
-  <si>
-    <t>MZ</t>
-  </si>
-  <si>
-    <t>acquisition</t>
-  </si>
-  <si>
-    <t>PZ_center</t>
-  </si>
-  <si>
-    <t>MZ_center</t>
-  </si>
-  <si>
-    <t>stt_near_321</t>
-  </si>
-  <si>
-    <t>data/td_raw/TD001_lct_heat_beta30_acq/output_all_time.dat</t>
-  </si>
-  <si>
-    <t>data/femap_raw/TD001_lct_heat_beta30_acq/model.modfem</t>
-  </si>
-  <si>
-    <t>data/femap_raw/TD001_lct_heat_beta30_acq/translation_rotation.xlsx</t>
-  </si>
-  <si>
-    <t>results/TD001_lct_heat_beta30_acq/los_angles.csv</t>
-  </si>
-  <si>
-    <t>Example: 3-orbit LEO case with local LCT heat, exported every 600 s. Use STT-relative LOS as main target.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -192,24 +67,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -497,178 +431,282 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="21.875" customWidth="1"/>
-    <col min="8" max="8" width="14.875" customWidth="1"/>
-    <col min="9" max="9" width="21.625" customWidth="1"/>
-    <col min="10" max="10" width="15.25" customWidth="1"/>
-    <col min="11" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="16.375" customWidth="1"/>
-    <col min="13" max="13" width="17.125" customWidth="1"/>
-    <col min="14" max="14" width="18.625" customWidth="1"/>
-    <col min="15" max="15" width="17.75" customWidth="1"/>
-    <col min="16" max="16" width="21" customWidth="1"/>
-    <col min="17" max="19" width="42" customWidth="1"/>
-    <col min="20" max="20" width="24.375" customWidth="1"/>
-    <col min="21" max="21" width="23.5" customWidth="1"/>
-    <col min="22" max="23" width="42" customWidth="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16.5" customWidth="1" min="2" max="2"/>
+    <col width="17.75" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16.875" customWidth="1" min="5" max="5"/>
+    <col width="18.5" customWidth="1" min="6" max="6"/>
+    <col width="21.875" customWidth="1" min="7" max="7"/>
+    <col width="14.875" customWidth="1" min="8" max="8"/>
+    <col width="21.625" customWidth="1" min="9" max="9"/>
+    <col width="15.25" customWidth="1" min="10" max="10"/>
+    <col width="16.875" customWidth="1" min="11" max="11"/>
+    <col width="16.375" customWidth="1" min="12" max="12"/>
+    <col width="17.125" customWidth="1" min="13" max="13"/>
+    <col width="18.625" customWidth="1" min="14" max="14"/>
+    <col width="17.75" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="19"/>
+    <col width="24.375" customWidth="1" min="20" max="20"/>
+    <col width="23.5" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="22" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>case_group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>use_for_model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>thermal_case</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>orbit_case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>beta_angle_deg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sun_direction_body</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>duration_s</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sample_interval_s</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>orbit_period_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>eclipse_entry_time_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>eclipse_exit_time_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>eclipse_duration_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>sunlit_duration_s</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>power_mode</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lct_heat_w</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>stt_heat_w</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pcdu_heat_w</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>stt_location</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>lct_location</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>constraint_set</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>td_output_path</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>femap_model_path</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>femap_result_path</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>femap_loadset_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>femap_loadset_end</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>python_result_path</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TD001_lct_heat_beta30_acq</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>local_heat</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>leo_3orbit_nominal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>16200</v>
+      </c>
+      <c r="I2" t="n">
+        <v>600</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="R2" t="n">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2">
-        <v>16200</v>
-      </c>
-      <c r="I2">
-        <v>600</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
-      <c r="L2">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>PZ_center</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>MZ_center</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>stt_near_321</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>data/td_raw/TD001_lct_heat_beta30_acq/output_all_time.dat</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>data/femap_raw/TD001_lct_heat_beta30_acq/model.modfem</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>data/femap_raw/TD001_lct_heat_beta30_acq/translation_rotation.xlsx</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
-      <c r="M2">
-        <v>12</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Z2" t="n">
         <v>32</v>
       </c>
-      <c r="Q2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2">
-        <v>2</v>
-      </c>
-      <c r="U2">
-        <v>32</v>
-      </c>
-      <c r="V2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" t="s">
-        <v>37</v>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>results/TD001_lct_heat_beta30_acq/los_angles.csv</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Example: 3-orbit LEO case with local LCT heat, exported every 600 s. Use STT-relative LOS as main target.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="2"/>
+  <autoFilter ref="A1:W2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>